--- a/Reports/FIO/Certificate/Certificate.xlsx
+++ b/Reports/FIO/Certificate/Certificate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenServer\domains\REPORTS-test\Reports\FIO\Certificate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1621F799-A104-4979-9650-3BBBC4331F66}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D40A10-1839-4AC4-BE08-FA060B12E42A}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="45" windowWidth="28560" windowHeight="12600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,10 +84,10 @@
     <t>"в том, что он (она) действительно зарегистрирован(а) в  ".$this-&gt;H['pref_region']." " .$this-&gt;H['name_region']</t>
   </si>
   <si>
-    <t>Информация не является исчерпывающей, в связи с всиуплением в силу приказа МВД России</t>
-  </si>
-  <si>
     <t>№984 от  31.12.2017 г.</t>
+  </si>
+  <si>
+    <t>Информация не является исчерпывающей, в связи с вступлением в силу приказа МВД России</t>
   </si>
 </sst>
 </file>
@@ -192,6 +192,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -207,9 +210,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -575,15 +575,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="11" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="11"/>
+      <c r="E1" s="12"/>
       <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
@@ -601,70 +601,70 @@
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="15" t="s">
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="15"/>
+      <c r="E2" s="16"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="3"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="3"/>
     </row>
     <row r="4" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="13" t="s">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="13"/>
+      <c r="E4" s="14"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="3"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="12" t="s">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="16"/>
+      <c r="E5" s="17"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="3"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="3"/>
     </row>
     <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
     </row>
     <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
@@ -684,12 +684,12 @@
     </row>
     <row r="10" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
       <c r="F10" s="7"/>
       <c r="G10" s="8" t="s">
         <v>1</v>
@@ -745,8 +745,8 @@
       <c r="E12" s="5"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>19</v>
+      <c r="A13" s="11" t="s">
+        <v>20</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -754,8 +754,8 @@
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>20</v>
+      <c r="A14" s="11" t="s">
+        <v>19</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -763,14 +763,14 @@
       <c r="E14" s="5"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="18"/>
+      <c r="A15" s="11"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="11" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="5"/>
